--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.46093657771526</v>
+        <v>3.81240219387873</v>
       </c>
       <c r="D2" t="n">
-        <v>23.54126531229588</v>
+        <v>3.82545561324808</v>
       </c>
       <c r="E2" t="n">
-        <v>5.565453141431219</v>
+        <v>0.9043861354825733</v>
       </c>
       <c r="F2" t="n">
-        <v>6.944641074685991</v>
+        <v>1.128504174636474</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.22252934360705</v>
+        <v>4.098661018336147</v>
       </c>
       <c r="D3" t="n">
-        <v>22.00568108466539</v>
+        <v>3.575923176258125</v>
       </c>
       <c r="E3" t="n">
-        <v>5.565453141431219</v>
+        <v>0.9043861354825733</v>
       </c>
       <c r="F3" t="n">
-        <v>6.944641074685991</v>
+        <v>1.128504174636474</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.78016139953958</v>
+        <v>2.564276227425182</v>
       </c>
       <c r="D4" t="n">
-        <v>16.76673505665366</v>
+        <v>2.72459444670622</v>
       </c>
       <c r="E4" t="n">
-        <v>5.565453141431219</v>
+        <v>0.9043861354825733</v>
       </c>
       <c r="F4" t="n">
-        <v>6.944641074685991</v>
+        <v>1.128504174636474</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.12309126422711</v>
+        <v>4.245002330436905</v>
       </c>
       <c r="D5" t="n">
-        <v>25.34758371127315</v>
+        <v>4.118982353081887</v>
       </c>
       <c r="E5" t="n">
-        <v>5.565453141431219</v>
+        <v>0.9043861354825733</v>
       </c>
       <c r="F5" t="n">
-        <v>6.944641074685991</v>
+        <v>1.128504174636474</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.15493930020081</v>
+        <v>5.387677636282632</v>
       </c>
       <c r="D6" t="n">
-        <v>37.7346072793779</v>
+        <v>6.13187368289891</v>
       </c>
       <c r="E6" t="n">
-        <v>5.565453141431219</v>
+        <v>0.9043861354825733</v>
       </c>
       <c r="F6" t="n">
-        <v>6.944641074685991</v>
+        <v>1.128504174636474</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
